--- a/ig/TEST-SUPPLEMENT/CodeSystem-RoleCode-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-RoleCode-supplement-fr.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/example/CodeSystem/RoleCode-supplement-fr</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/roleCode-supplement-fr</t>
   </si>
   <si>
     <t>Version</t>

--- a/ig/TEST-SUPPLEMENT/CodeSystem-RoleCode-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-RoleCode-supplement-fr.xlsx
@@ -72,7 +72,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Traduction Francaise</t>
+    <t>Traduction Française</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ig/TEST-SUPPLEMENT/CodeSystem-RoleCode-supplement-fr.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-RoleCode-supplement-fr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>AUNT</t>
-  </si>
-  <si>
-    <t>BRO</t>
   </si>
   <si>
     <t>BROINLAW</t>
@@ -766,7 +763,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1923,16 +1920,6 @@
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
     </row>
-    <row r="116">
-      <c r="A116" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
